--- a/documentacao-vooh/gestao_de_acessos/gestao_de_acesso-VOOH.xlsx
+++ b/documentacao-vooh/gestao_de_acessos/gestao_de_acesso-VOOH.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\V-OOH\documentacao-vooh\gestao_de_acessos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63FAAD4F-5E4B-43B5-8AC0-93A71FBB21DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A23C59B9-95A8-4E8A-BE4A-269065DA4E52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{D1B643D6-2457-402A-92A1-FB8FF4804C55}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="73">
   <si>
     <t>Ocorrência</t>
   </si>
@@ -90,9 +90,6 @@
     <t>Mudança nos parâmetros padrão de coleta de métricas</t>
   </si>
   <si>
-    <t>✅</t>
-  </si>
-  <si>
     <t>❌</t>
   </si>
   <si>
@@ -232,6 +229,21 @@
   </si>
   <si>
     <t>Política de Gestão de Acessos</t>
+  </si>
+  <si>
+    <t>RWE</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>R--</t>
+  </si>
+  <si>
+    <t>R-E</t>
+  </si>
+  <si>
+    <t>~WE</t>
   </si>
 </sst>
 </file>
@@ -268,20 +280,6 @@
       <family val="2"/>
     </font>
     <font>
-      <u/>
-      <sz val="12"/>
-      <color theme="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b/>
       <sz val="12"/>
       <color theme="0"/>
@@ -293,6 +291,17 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="7">
@@ -389,13 +398,10 @@
   </cellStyleXfs>
   <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -410,47 +416,50 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -791,734 +800,734 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
+      <c r="A1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
     </row>
     <row r="2" spans="1:7" s="2" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G9" s="13" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" s="11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A4" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="G4" s="16" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="G5" s="11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="75" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6" s="16" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="75" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="G7" s="11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="75" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="21" t="s">
+      <c r="B10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="F10" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="G10" s="21" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="F12" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="G12" s="21" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="F8" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8" s="16" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="F9" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="G9" s="11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="105" x14ac:dyDescent="0.25">
-      <c r="A10" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="E10" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="F10" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="G10" s="14" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" s="7" t="s">
+      <c r="C14" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="E14" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="F14" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="G14" s="21" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="75" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12" s="12" t="s">
+      <c r="B15" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A16" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="E12" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="F12" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="G12" s="14" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="75" x14ac:dyDescent="0.25">
-      <c r="A14" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="C14" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="E14" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="F14" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="G14" s="14" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="B15" s="7" t="s">
+      <c r="B16" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="E16" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="F16" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="G16" s="21" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F17" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G17" s="13" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="D18" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="E18" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="F18" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="G18" s="16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F19" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G19" s="13" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C15" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="G15" s="9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A16" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="C16" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="D16" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="E16" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="F16" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="G16" s="14" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="F17" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="G17" s="11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="75" x14ac:dyDescent="0.25">
-      <c r="A18" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="C18" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="D18" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="E18" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="F18" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="G18" s="16" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E19" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="F19" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="G19" s="11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A20" s="12" t="s">
+      <c r="B20" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="12" t="s">
+      <c r="C20" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="E20" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="F20" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="G20" s="21" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A21" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C20" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="D20" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="E20" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="F20" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="G20" s="14" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
+      <c r="B21" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="C21" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="E21" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F21" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G21" s="13" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A22" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C21" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E21" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="F21" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="G21" s="11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A22" s="12" t="s">
+      <c r="B22" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="B22" s="12" t="s">
+      <c r="C22" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="D22" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="E22" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="G22" s="16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A23" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="C22" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="D22" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="E22" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="F22" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="G22" s="16" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="s">
+      <c r="B23" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="C23" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="F23" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G23" s="13" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A24" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="C23" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="F23" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="G23" s="11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="75" x14ac:dyDescent="0.25">
-      <c r="A24" s="12" t="s">
+      <c r="B24" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="B24" s="12" t="s">
+      <c r="C24" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="D24" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="E24" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="F24" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="G24" s="16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A25" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="C24" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="D24" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="E24" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="F24" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="G24" s="16" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="s">
+      <c r="B25" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="C25" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F25" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G25" s="13" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A26" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="C25" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E25" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="F25" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="G25" s="11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A26" s="12" t="s">
+      <c r="B26" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="B26" s="12" t="s">
+      <c r="C26" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="D26" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="E26" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="F26" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="G26" s="16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A27" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="C26" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="D26" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="E26" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="F26" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="G26" s="16" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A27" s="7" t="s">
+      <c r="B27" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="C27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G27" s="13" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A28" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="C27" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="D27" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E27" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="F27" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="G27" s="11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A28" s="12" t="s">
+      <c r="B28" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B28" s="12" t="s">
+      <c r="C28" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D28" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="E28" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="F28" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="G28" s="18" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A29" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="C28" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="D28" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="E28" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="F28" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="G28" s="18" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A29" s="7" t="s">
+      <c r="B29" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="C29" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="E29" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="F29" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="G29" s="20" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A30" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="C29" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="D29" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E29" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="F29" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="G29" s="20" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A30" s="12" t="s">
+      <c r="B30" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="B30" s="12" t="s">
+      <c r="C30" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D30" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="E30" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="F30" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="G30" s="18" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A31" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="C30" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="D30" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="E30" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="F30" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="G30" s="18" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="75" x14ac:dyDescent="0.25">
-      <c r="A31" s="7" t="s">
+      <c r="B31" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B31" s="7" t="s">
+      <c r="C31" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="E31" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="F31" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="G31" s="10" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A32" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="C31" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="D31" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E31" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="F31" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="G31" s="9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A32" s="12" t="s">
+      <c r="B32" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="B32" s="12" t="s">
-        <v>67</v>
-      </c>
       <c r="C32" s="17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D32" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="E32" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="F32" s="14" t="s">
-        <v>21</v>
+        <v>21</v>
+      </c>
+      <c r="E32" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="F32" s="21" t="s">
+        <v>70</v>
       </c>
       <c r="G32" s="18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
 </worksheet>
